--- a/Configs/GameConfig/Datas/wave_plan.xlsx
+++ b/Configs/GameConfig/Datas/wave_plan.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rea77d200c78e4145"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89eb49265f324171"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -574,21 +574,23 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="D6" t="str">
-        <x:v>Normal</x:v>
+        <x:v>Boss</x:v>
       </x:c>
       <x:c r="E6"/>
       <x:c r="F6" t="n">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H6"/>
+      <x:c r="H6" t="str">
+        <x:v>ZhangLiang</x:v>
+      </x:c>
       <x:c r="I6" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" t="n">
-        <x:v>1500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K6" t="n">
         <x:v>10000</x:v>
@@ -597,7 +599,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M6" s="1" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N6" t="n">
         <x:v>0</x:v>

--- a/Configs/GameConfig/Datas/wave_plan.xlsx
+++ b/Configs/GameConfig/Datas/wave_plan.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R89eb49265f324171"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R75dbbf1d42c3465d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -356,7 +356,7 @@
         <x:v>##var</x:v>
       </x:c>
       <x:c r="B1" t="str">
-        <x:v>planId</x:v>
+        <x:v>id</x:v>
       </x:c>
       <x:c r="C1" t="str">
         <x:v>order</x:v>
@@ -365,7 +365,7 @@
         <x:v>kind</x:v>
       </x:c>
       <x:c r="E1" t="str">
-        <x:v>enemyKey</x:v>
+        <x:v>enemyId</x:v>
       </x:c>
       <x:c r="F1" t="str">
         <x:v>normalCount</x:v>
@@ -374,7 +374,7 @@
         <x:v>difficultyIndex</x:v>
       </x:c>
       <x:c r="H1" t="str">
-        <x:v>bossKey</x:v>
+        <x:v>bossId</x:v>
       </x:c>
       <x:c r="I1" t="str">
         <x:v>preDelayMs</x:v>
@@ -394,13 +394,14 @@
       <x:c r="N1" t="str">
         <x:v>strategyProfile</x:v>
       </x:c>
+      <x:c r="O1"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" t="str">
         <x:v>##type</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>string</x:v>
+        <x:v>int</x:v>
       </x:c>
       <x:c r="C2" t="str">
         <x:v>int</x:v>
@@ -409,7 +410,7 @@
         <x:v>battle.EWaveKind</x:v>
       </x:c>
       <x:c r="E2" t="str">
-        <x:v>string</x:v>
+        <x:v>int?</x:v>
       </x:c>
       <x:c r="F2" t="str">
         <x:v>int</x:v>
@@ -418,7 +419,7 @@
         <x:v>int</x:v>
       </x:c>
       <x:c r="H2" t="str">
-        <x:v>string</x:v>
+        <x:v>int?</x:v>
       </x:c>
       <x:c r="I2" t="str">
         <x:v>long</x:v>
@@ -438,13 +439,14 @@
       <x:c r="N2" t="str">
         <x:v>int</x:v>
       </x:c>
+      <x:c r="O2"/>
     </x:row>
     <x:row r="3">
       <x:c r="A3" t="str">
         <x:v>##</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>计划ID</x:v>
+        <x:v>计划ID(联合主键1，供 wave.activePlanId 选择)</x:v>
       </x:c>
       <x:c r="C3" t="str">
         <x:v>波次顺序</x:v>
@@ -482,6 +484,7 @@
       <x:c r="N3" t="str">
         <x:v>逐波策略配置</x:v>
       </x:c>
+      <x:c r="O3"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" t="str">
@@ -526,11 +529,12 @@
       <x:c r="N4" t="str">
         <x:v>c</x:v>
       </x:c>
+      <x:c r="O4"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5"/>
-      <x:c r="B5" t="str">
-        <x:v>default</x:v>
+      <x:c r="B5" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C5" t="n">
         <x:v>1</x:v>
@@ -564,11 +568,12 @@
       <x:c r="N5" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O5"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6"/>
-      <x:c r="B6" t="str">
-        <x:v>default</x:v>
+      <x:c r="B6" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C6" t="n">
         <x:v>2</x:v>
@@ -583,8 +588,8 @@
       <x:c r="G6" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H6" t="str">
-        <x:v>ZhangLiang</x:v>
+      <x:c r="H6" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I6" t="n">
         <x:v>0</x:v>
@@ -604,11 +609,12 @@
       <x:c r="N6" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O6"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7"/>
-      <x:c r="B7" t="str">
-        <x:v>default</x:v>
+      <x:c r="B7" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C7" t="n">
         <x:v>3</x:v>
@@ -642,11 +648,12 @@
       <x:c r="N7" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O7"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8"/>
-      <x:c r="B8" t="str">
-        <x:v>default</x:v>
+      <x:c r="B8" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C8" t="n">
         <x:v>4</x:v>
@@ -680,11 +687,12 @@
       <x:c r="N8" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O8"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9"/>
-      <x:c r="B9" t="str">
-        <x:v>default</x:v>
+      <x:c r="B9" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C9" t="n">
         <x:v>5</x:v>
@@ -718,11 +726,12 @@
       <x:c r="N9" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O9"/>
     </x:row>
     <x:row r="10">
       <x:c r="A10"/>
-      <x:c r="B10" t="str">
-        <x:v>default</x:v>
+      <x:c r="B10" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C10" t="n">
         <x:v>6</x:v>
@@ -756,11 +765,12 @@
       <x:c r="N10" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O10"/>
     </x:row>
     <x:row r="11">
       <x:c r="A11"/>
-      <x:c r="B11" t="str">
-        <x:v>default</x:v>
+      <x:c r="B11" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C11" t="n">
         <x:v>7</x:v>
@@ -794,11 +804,12 @@
       <x:c r="N11" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O11"/>
     </x:row>
     <x:row r="12">
       <x:c r="A12"/>
-      <x:c r="B12" t="str">
-        <x:v>default</x:v>
+      <x:c r="B12" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C12" t="n">
         <x:v>8</x:v>
@@ -832,11 +843,12 @@
       <x:c r="N12" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O12"/>
     </x:row>
     <x:row r="13">
       <x:c r="A13"/>
-      <x:c r="B13" t="str">
-        <x:v>default</x:v>
+      <x:c r="B13" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C13" t="n">
         <x:v>9</x:v>
@@ -870,11 +882,12 @@
       <x:c r="N13" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O13"/>
     </x:row>
     <x:row r="14">
       <x:c r="A14"/>
-      <x:c r="B14" t="str">
-        <x:v>default</x:v>
+      <x:c r="B14" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C14" t="n">
         <x:v>10</x:v>
@@ -889,8 +902,8 @@
       <x:c r="G14" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="H14" t="str">
-        <x:v>ZhangLiang</x:v>
+      <x:c r="H14" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="I14" t="n">
         <x:v>0</x:v>
@@ -910,11 +923,12 @@
       <x:c r="N14" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O14"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15"/>
-      <x:c r="B15" t="str">
-        <x:v>default</x:v>
+      <x:c r="B15" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C15" t="n">
         <x:v>11</x:v>
@@ -948,11 +962,12 @@
       <x:c r="N15" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O15"/>
     </x:row>
     <x:row r="16">
       <x:c r="A16"/>
-      <x:c r="B16" t="str">
-        <x:v>default</x:v>
+      <x:c r="B16" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C16" t="n">
         <x:v>12</x:v>
@@ -986,11 +1001,12 @@
       <x:c r="N16" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O16"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17"/>
-      <x:c r="B17" t="str">
-        <x:v>default</x:v>
+      <x:c r="B17" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C17" t="n">
         <x:v>13</x:v>
@@ -1024,11 +1040,12 @@
       <x:c r="N17" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O17"/>
     </x:row>
     <x:row r="18">
       <x:c r="A18"/>
-      <x:c r="B18" t="str">
-        <x:v>default</x:v>
+      <x:c r="B18" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C18" t="n">
         <x:v>14</x:v>
@@ -1062,11 +1079,12 @@
       <x:c r="N18" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O18"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19"/>
-      <x:c r="B19" t="str">
-        <x:v>default</x:v>
+      <x:c r="B19" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C19" t="n">
         <x:v>15</x:v>
@@ -1100,11 +1118,12 @@
       <x:c r="N19" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O19"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20"/>
-      <x:c r="B20" t="str">
-        <x:v>default</x:v>
+      <x:c r="B20" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C20" t="n">
         <x:v>16</x:v>
@@ -1138,11 +1157,12 @@
       <x:c r="N20" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O20"/>
     </x:row>
     <x:row r="21">
       <x:c r="A21"/>
-      <x:c r="B21" t="str">
-        <x:v>default</x:v>
+      <x:c r="B21" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C21" t="n">
         <x:v>17</x:v>
@@ -1176,11 +1196,12 @@
       <x:c r="N21" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O21"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22"/>
-      <x:c r="B22" t="str">
-        <x:v>default</x:v>
+      <x:c r="B22" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C22" t="n">
         <x:v>18</x:v>
@@ -1214,11 +1235,12 @@
       <x:c r="N22" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O22"/>
     </x:row>
     <x:row r="23">
       <x:c r="A23"/>
-      <x:c r="B23" t="str">
-        <x:v>default</x:v>
+      <x:c r="B23" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C23" t="n">
         <x:v>19</x:v>
@@ -1252,11 +1274,12 @@
       <x:c r="N23" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O23"/>
     </x:row>
     <x:row r="24">
       <x:c r="A24"/>
-      <x:c r="B24" t="str">
-        <x:v>default</x:v>
+      <x:c r="B24" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C24" t="n">
         <x:v>20</x:v>
@@ -1290,11 +1313,12 @@
       <x:c r="N24" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O24"/>
     </x:row>
     <x:row r="25">
       <x:c r="A25"/>
-      <x:c r="B25" t="str">
-        <x:v>default</x:v>
+      <x:c r="B25" t="n">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C25" t="n">
         <x:v>21</x:v>
@@ -1328,6 +1352,7 @@
       <x:c r="N25" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="O25"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Configs/GameConfig/Datas/wave_plan.xlsx
+++ b/Configs/GameConfig/Datas/wave_plan.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R75dbbf1d42c3465d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdd6901f2582c41aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -446,43 +446,43 @@
         <x:v>##</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>计划ID(联合主键1，供 wave.activePlanId 选择)</x:v>
+        <x:v>计划 ID，应与 wave.activePlanId 一致</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>波次顺序</x:v>
+        <x:v>波次顺序，从 1 开始连续递增，不可重复、不可跳号</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>波次类型</x:v>
+        <x:v>波次类型：Normal=普通波 / Boss=Boss 波</x:v>
       </x:c>
       <x:c r="E3" t="str">
-        <x:v>普通敌人Key</x:v>
+        <x:v>Normal 波的敌人 ID，留空时使用地图的 EnemyId</x:v>
       </x:c>
       <x:c r="F3" t="str">
-        <x:v>普通敌人数量</x:v>
+        <x:v>Normal 波怪物数量，Boss 波填 0</x:v>
       </x:c>
       <x:c r="G3" t="str">
-        <x:v>难度索引</x:v>
+        <x:v>难度索引，索引 enemystats.healthByWave，从 0 开始</x:v>
       </x:c>
       <x:c r="H3" t="str">
-        <x:v>Boss敌人Key</x:v>
+        <x:v>Boss 波必填的 Boss ID，Normal 波留空</x:v>
       </x:c>
       <x:c r="I3" t="str">
-        <x:v>前置延迟(毫秒)</x:v>
+        <x:v>本波开始前的等待时间，毫秒</x:v>
       </x:c>
       <x:c r="J3" t="str">
-        <x:v>刷怪间隔(毫秒)</x:v>
+        <x:v>普通怪之间的出生间隔，毫秒</x:v>
       </x:c>
       <x:c r="K3" t="str">
-        <x:v>后置延迟(毫秒)</x:v>
+        <x:v>本波结束后的等待时间，毫秒</x:v>
       </x:c>
       <x:c r="L3" t="str">
-        <x:v>玩家侧是否出怪</x:v>
+        <x:v>玩家侧是否生成</x:v>
       </x:c>
       <x:c r="M3" t="str">
-        <x:v>对手侧是否出怪</x:v>
+        <x:v>对手侧是否生成，至少一侧必须为 true</x:v>
       </x:c>
       <x:c r="N3" t="str">
-        <x:v>逐波策略配置</x:v>
+        <x:v>生成策略索引，引用 wave.spawnStrategies 的行，从 0 开始</x:v>
       </x:c>
       <x:c r="O3"/>
     </x:row>
